--- a/src/main/resources/templates/用户导入模板.xlsx
+++ b/src/main/resources/templates/用户导入模板.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>用户名</t>
   </si>
@@ -78,10 +78,7 @@
     <t>邮箱</t>
   </si>
   <si>
-    <t>机构名称</t>
-  </si>
-  <si>
-    <t>部门名称</t>
+    <t>部门编码</t>
   </si>
   <si>
     <t>角色名称</t>
@@ -1269,17 +1266,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="2" width="17.5583333333333" style="1" customWidth="1"/>
     <col min="3" max="3" width="13.1083333333333" style="1" customWidth="1"/>
     <col min="4" max="4" width="17.5583333333333" style="1" customWidth="1"/>
     <col min="5" max="5" width="26" style="1" customWidth="1"/>
-    <col min="6" max="8" width="17.5583333333333" style="1" customWidth="1"/>
+    <col min="6" max="7" width="17.5583333333333" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:7">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1300,9 +1297,6 @@
       </c>
       <c r="G1" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/templates/用户导入模板.xlsx
+++ b/src/main/resources/templates/用户导入模板.xlsx
@@ -56,12 +56,24 @@
         </r>
       </text>
     </comment>
+    <comment ref="G1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>必填</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>用户名</t>
   </si>
@@ -78,7 +90,10 @@
     <t>邮箱</t>
   </si>
   <si>
-    <t>部门编码</t>
+    <t>机构名称</t>
+  </si>
+  <si>
+    <t>部门名称</t>
   </si>
   <si>
     <t>角色名称</t>
@@ -1266,17 +1281,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="2" width="17.5583333333333" style="1" customWidth="1"/>
     <col min="3" max="3" width="13.1083333333333" style="1" customWidth="1"/>
     <col min="4" max="4" width="17.5583333333333" style="1" customWidth="1"/>
     <col min="5" max="5" width="26" style="1" customWidth="1"/>
-    <col min="6" max="7" width="17.5583333333333" style="1" customWidth="1"/>
+    <col min="6" max="8" width="17.5583333333333" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1297,6 +1312,9 @@
       </c>
       <c r="G1" s="2" t="s">
         <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
